--- a/data/exports/stress_analysis_2026-05-14.xlsx
+++ b/data/exports/stress_analysis_2026-05-14.xlsx
@@ -431,13 +431,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -494,20 +494,24 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-14 12:13:27</t>
+          <t>2026-04-29 22:09:56</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>75.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>376</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>0.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -515,36 +519,2845 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>hr_10s</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-29 23:18:11</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-29 23:18:41</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:34:02</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:53:49</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>303.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-11 17:56:09</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-11 17:56:39</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>121</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9907.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-11 17:58:09</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1144.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:13:27</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2026-05-14 12:13:37</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C11" t="n">
         <v>66.8</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
         <v>0.83</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>rppg_face</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:29:26</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:29:36</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:29:46</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:29:56</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:30:06</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:30:16</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:30:26</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:30:36</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:30:46</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:30:56</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:31:06</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:31:16</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:31:26</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:31:36</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:31:46</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:31:56</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:32:06</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>69</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:32:16</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:32:26</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:39:03</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:39:13</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:39:23</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:39:33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:39:43</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:39:53</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:40:03</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:40:13</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:40:23</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:40:33</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:40:43</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:40:53</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:41:03</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:41:13</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:41:23</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:41:33</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:41:43</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:41:53</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:42:03</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:42:13</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:42:23</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:42:33</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:42:43</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:42:53</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:03</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:13</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:23</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:33</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:43</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:53</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>hrv_5min</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:53</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:44:03</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:44:13</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:44:23</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>68</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:44:33</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:44:43</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:44:53</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:45:03</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:45:13</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:45:23</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:45:33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:45:43</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:45:53</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:46:03</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:46:13</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:46:23</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:46:33</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:46:43</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:46:53</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>89</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:47:03</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:47:13</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:47:23</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:47:33</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>54</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:47:43</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>68</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:47:53</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>64</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:03</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:13</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:23</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:33</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:43</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:53</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>hrv_5min</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:53</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:49:03</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>57</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:49:13</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:49:23</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:49:33</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:49:43</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:49:53</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:50:03</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>hr_10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:50:13</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>rppg_face</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
         <is>
           <t>hr_10s</t>
         </is>
@@ -561,11 +3374,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -628,6 +3441,1414 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:28:27</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-104.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:28:57</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="E3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:29:27</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="E4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-29 23:16:04</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-29 23:16:35</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="E6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-30 01:24:01</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>34</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-106.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:27:45</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="E8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-66.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:28:15</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-91</v>
+      </c>
+      <c r="H9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:28:45</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="E10" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:29:15</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="E11" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:29:45</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="E12" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-34.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:30:15</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-128.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:30:45</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-92.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:31:15</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E15" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:54:47</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-74.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:57:15</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="E17" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-33.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:29:46</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-30.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:30:16</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>36</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="E19" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-51.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:30:46</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="E20" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-39.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:31:16</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="E21" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-57.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>106</v>
+      </c>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:31:46</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>22</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="E22" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-61.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:32:16</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>14</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="E23" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-77.90000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:39:23</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-57.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.186</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:39:53</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="E25" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>100</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:40:23</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-108.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:40:53</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E27" t="n">
+        <v>21</v>
+      </c>
+      <c r="F27" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-166.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.089</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:41:23</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-140.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:41:53</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>36</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:42:23</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>14</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="E30" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.261</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:42:53</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="E31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-56.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.244</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:23</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E32" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-139.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.004</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:53</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="E33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-98.2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:44:23</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>14</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-113.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:44:53</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E35" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-111.2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:45:23</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="E36" t="n">
+        <v>17</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-27.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:45:53</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-50.3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:46:23</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E38" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-102.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.218</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:46:53</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>26</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:47:23</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>22</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E40" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-75.40000000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.276</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:47:53</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>16</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="E41" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-71</v>
+      </c>
+      <c r="H41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:23</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>26</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-98.3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.304</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:53</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>32</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="E43" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="G43" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:49:23</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="E44" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-24.4</v>
+      </c>
+      <c r="G44" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="H44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.459</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:49:53</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="E45" t="n">
+        <v>20</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.204</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.287</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -639,15 +4860,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -686,6 +4907,1282 @@
         <is>
           <t>window_switches</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:25:53</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>view_data.py - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:27:33</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C:\Users\dimit\Desktop\msc_thesis\stress_detection\venv\Scripts\python.exe</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:28:03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>desktop_monitor</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:28:33</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apps and websites - Claude - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:29:03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Face Monitor â€” Q to quit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:29:33</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Face Monitor â€” Q to quit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:30:03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Face Monitor â€” Q to quit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:30:33</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Face Monitor â€” Q to quit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>80</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-30T11:31:03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Snipping Tool</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-11T14:55:48</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>main.dart - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:11:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>desktop_monitor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:12:15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rppg_monitor.py - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:12:45</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>rppg_monitor.py - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:13:15</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rppg_monitor.py - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:13:45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>rppg_monitor.py - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:14:15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>desktop_monitor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" t="n">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:29:47</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Μεταπτυχιακό Πληροφοριακά Συστήματα και Υπηρεσίες and 1 more page - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:30:17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>New tab and 2 more pages - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:30:47</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Stress Monitor -- Q to quit</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:31:17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Save As</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:31:47</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Save As</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:32:17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>config.py - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:39:23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:39:53</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" t="n">
+        <v>63.33333333333333</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:40:23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:40:53</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:41:23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>17</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:41:53</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>22</v>
+      </c>
+      <c r="F29" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:42:23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>17</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:42:53</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:43:23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:43:53</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>90</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:44:23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:44:53</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>70</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:45:23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>config.py - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:45:53</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>config.py - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:46:23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:46:53</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Build shared camera feed… - stress_detection - Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>IDE/Terminal</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>27</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:47:23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>15</v>
+      </c>
+      <c r="F40" t="n">
+        <v>50</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:47:53</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>80</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:48:23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:48:53</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F43" t="n">
+        <v>70</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:49:23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-14T23:49:53</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Πλατφόρμα e-learning MELO - Digital Learning Ecosystem - Personal - Microsoft​ Edge</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>16</v>
+      </c>
+      <c r="F45" t="n">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -699,7 +6196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -845,6 +6342,102 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:38:53</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:53</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>69.70699999999999</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>16.889</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18.867</v>
+      </c>
+      <c r="L3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:43:53</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:48:53</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>66.542</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="R4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1049,19 +6642,35 @@
           <t>avg_hr</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1109,19 +6718,35 @@
           <t>avg_blink_rate</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1129,19 +6754,35 @@
           <t>avg_ear</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>-1</v>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1149,19 +6790,35 @@
           <t>avg_valence</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1169,19 +6826,35 @@
           <t>avg_arousal</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1189,19 +6862,35 @@
           <t>avg_pitch</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1209,19 +6898,35 @@
           <t>avg_yaw</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1289,19 +6994,35 @@
           <t>stress_index</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1314,16 +7035,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>avg_hr</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>avg_blink_rate</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>avg_ear</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>avg_valence</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>avg_arousal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>stress_index</t>
         </is>
       </c>
@@ -1335,7 +7086,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1345,7 +7111,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>68.124</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16.044</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="4">
@@ -1354,7 +7135,24 @@
           <t>std</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>2.238</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.014</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1363,6 +7161,21 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>66.542</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1373,7 +7186,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>67.333</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15.622</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="7">
@@ -1383,7 +7211,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>68.124</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16.044</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="8">
@@ -1393,7 +7236,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>68.916</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16.467</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="9">
@@ -1403,7 +7261,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>69.70699999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16.889</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.026</v>
       </c>
     </row>
   </sheetData>
